--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6291.96</v>
+        <v>6257.57</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3494.08</v>
+        <v>3532.09</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>750.25</v>
+        <v>752.72</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6162.48</v>
+        <v>6206.91</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2353.72</v>
+        <v>2349.54</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7831.87</v>
+        <v>7817.98</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2997.09</v>
+        <v>3018.24</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>35685.86</v>
+        <v>35224.59</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3717.99</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1172.64</v>
+        <v>1180.71</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6094.01</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2180.96</v>
+        <v>2169.44</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1224.19</v>
+        <v>1222.09</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5186.5</v>
+        <v>5181.15</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10237.82</v>
+        <v>10406.55</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9465.01</v>
+        <v>9343.16</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3255.7</v>
+        <v>3213.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>816.51</v>
+        <v>831.3099999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1396.92</v>
+        <v>1400.99</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6684.99</v>
+        <v>6745.21</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>894.16</v>
+        <v>897.55</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3246.81</v>
+        <v>3259.11</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14215.71</v>
+        <v>14260.96</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>792.52</v>
+        <v>796.73</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34510.08</v>
+        <v>34693.59</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>782.33</v>
+        <v>793.52</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3738.41</v>
+        <v>3782.26</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14522.89</v>
+        <v>14768.51</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3582.4</v>
+        <v>3618.83</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22518.05</v>
+        <v>22747.05</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11399.12</v>
+        <v>11506.03</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1545.16</v>
+        <v>1552.17</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1204.62</v>
+        <v>1212.93</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5001.7</v>
+        <v>5034.3</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1197.59</v>
+        <v>1195.19</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>23130.85</v>
+        <v>23002.61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4631-131-CM25</t>
+          <t>411-8863-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6257.57</v>
+        <v>1066.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2380-2541-CM25</t>
+          <t>1079486-63-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3532.09</v>
+        <v>10283.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5349-2410-CM25</t>
+          <t>5349-1571-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>752.72</v>
+        <v>1178.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1228-32-CM25</t>
+          <t>5349-1603-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.804.005-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6206.91</v>
+        <v>1088.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2380-2634-CM25</t>
+          <t>2380-1750-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2349.54</v>
+        <v>3142.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2380-2635-CM25</t>
+          <t>2380-1788-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7817.98</v>
+        <v>4093.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5349-2466-CM25</t>
+          <t>4631-90-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3018.24</v>
+        <v>2043.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2380-2682-CM25</t>
+          <t>2380-2078-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>35224.59</v>
+        <v>15877.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>751-1552-CM25</t>
+          <t>2380-2297-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3681</v>
+        <v>5867.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2322-1934-CM25</t>
+          <t>4631-131-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1180.71</v>
+        <v>6257.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2380-32-CM26</t>
+          <t>2380-2541-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6082</v>
+        <v>3532.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2380-80-CM26</t>
+          <t>5349-2410-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2169.44</v>
+        <v>752.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2322-88-CM26</t>
+          <t>1228-32-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>60.804.005-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1222.09</v>
+        <v>6206.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2322-100-CM26</t>
+          <t>2380-2635-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5181.15</v>
+        <v>7817.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2380-374-CM26</t>
+          <t>2380-2634-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10406.55</v>
+        <v>2349.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1554-302-CM26</t>
+          <t>5349-2466-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9343.16</v>
+        <v>3018.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1554-303-CM26</t>
+          <t>2380-2682-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3213.78</v>
+        <v>35224.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2859-71-CM26</t>
+          <t>751-1552-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>831.3099999999999</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2381-443-CM26</t>
+          <t>2322-1934-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1400.99</v>
+        <v>1180.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2923-280-CM26</t>
+          <t>2380-32-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6745.21</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5349-929-CM26</t>
+          <t>2380-80-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>897.55</v>
+        <v>2169.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5349-935-CM26</t>
+          <t>2322-88-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3259.11</v>
+        <v>1222.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2380-946-CM26</t>
+          <t>2322-100-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14260.96</v>
+        <v>5181.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2381-641-CM26</t>
+          <t>2380-374-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>796.73</v>
+        <v>10406.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1027-38-CM26</t>
+          <t>1554-302-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34693.59</v>
+        <v>9343.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2322-378-CM26</t>
+          <t>1554-303-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>793.52</v>
+        <v>3213.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>904-61-CM26</t>
+          <t>2859-71-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3782.26</v>
+        <v>831.3099999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2322-393-CM26</t>
+          <t>2381-443-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14768.51</v>
+        <v>1400.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1172445-49-CM26</t>
+          <t>2923-280-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3618.83</v>
+        <v>6745.21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2380-1012-CM26</t>
+          <t>5349-929-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22747.05</v>
+        <v>897.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1027-39-CM26</t>
+          <t>5349-935-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11506.03</v>
+        <v>3259.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2322-433-CM26</t>
+          <t>2380-946-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1552.17</v>
+        <v>14260.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2859-576-CM26</t>
+          <t>1027-38-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1212.93</v>
+        <v>34693.59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>751-236-CM26</t>
+          <t>2381-641-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5034.3</v>
+        <v>796.73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5349-1418-CM26</t>
+          <t>2322-378-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1195.19</v>
+        <v>793.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1027-59-CM26</t>
+          <t>904-61-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,6 +2704,555 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
+        <v>3782.26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2322-393-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>14768.51</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1172445-49-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3618.83</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2380-1012-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>22747.05</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1027-39-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>11506.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2322-433-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1552.17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2859-576-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>1212.93</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>751-236-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>5034.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5349-1418-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL COMPARO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1195.19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1027-59-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>23002.61</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>411-8863-CM25</t>
+          <t>2380-35-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1066.74</v>
+        <v>7656.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079486-63-CM25</t>
+          <t>411-46-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10283.61</v>
+        <v>1608.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5349-1571-CM25</t>
+          <t>1554-348-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1178.84</v>
+        <v>4051.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5349-1603-CM25</t>
+          <t>2380-322-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1088.35</v>
+        <v>8110.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2380-1750-CM25</t>
+          <t>4190-56-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3142.37</v>
+        <v>9487.879999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2380-1788-CM25</t>
+          <t>2859-86-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4093.75</v>
+        <v>910.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4631-90-CM25</t>
+          <t>707416-24-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2043.57</v>
+        <v>1089.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2380-2078-CM25</t>
+          <t>2380-505-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>15877.21</v>
+        <v>11304.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2380-2297-CM25</t>
+          <t>1729-112-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5867.54</v>
+        <v>10796.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4631-131-CM25</t>
+          <t>1172445-139-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6257.57</v>
+        <v>51031.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2380-2541-CM25</t>
+          <t>1172445-132-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3532.09</v>
+        <v>4538.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5349-2410-CM25</t>
+          <t>1028871-821-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>752.72</v>
+        <v>4206.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1228-32-CM25</t>
+          <t>1554-674-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.804.005-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6206.91</v>
+        <v>10399.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2380-2635-CM25</t>
+          <t>2175-71-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7817.98</v>
+        <v>11972.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2380-2634-CM25</t>
+          <t>2380-789-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2349.54</v>
+        <v>5196.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5349-2466-CM25</t>
+          <t>411-8863-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3018.24</v>
+        <v>1066.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2380-2682-CM25</t>
+          <t>2380-878-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35224.59</v>
+        <v>11525.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>751-1552-CM25</t>
+          <t>2923-287-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3681</v>
+        <v>23459.55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2322-1934-CM25</t>
+          <t>1172445-2161-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1180.71</v>
+        <v>1703.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2380-32-CM26</t>
+          <t>1079486-63-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6082</v>
+        <v>10283.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2380-80-CM26</t>
+          <t>2380-1171-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2169.44</v>
+        <v>5997.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2322-88-CM26</t>
+          <t>2380-1180-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1222.09</v>
+        <v>11534.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2322-100-CM26</t>
+          <t>2380-1192-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.087.242-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5181.15</v>
+        <v>33816.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2380-374-CM26</t>
+          <t>2380-1423-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10406.55</v>
+        <v>17276.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1554-302-CM26</t>
+          <t>2859-845-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9343.16</v>
+        <v>1137.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1554-303-CM26</t>
+          <t>2380-1532-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3213.78</v>
+        <v>33768.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2859-71-CM26</t>
+          <t>2380-1544-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>831.3099999999999</v>
+        <v>5706.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2381-443-CM26</t>
+          <t>2175-169-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA  CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.575.038-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1400.99</v>
+        <v>40155.79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2923-280-CM26</t>
+          <t>2380-1578-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6745.21</v>
+        <v>6971.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5349-929-CM26</t>
+          <t>5349-1551-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>897.55</v>
+        <v>731.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5349-935-CM26</t>
+          <t>5349-1571-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3259.11</v>
+        <v>1178.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2380-946-CM26</t>
+          <t>5349-1603-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14260.96</v>
+        <v>1088.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1027-38-CM26</t>
+          <t>2923-418-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>34693.59</v>
+        <v>11616.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2381-641-CM26</t>
+          <t>2380-1750-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>796.73</v>
+        <v>3142.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2322-378-CM26</t>
+          <t>2923-433-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>793.52</v>
+        <v>2246.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>904-61-CM26</t>
+          <t>2380-1788-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3782.26</v>
+        <v>4093.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2322-393-CM26</t>
+          <t>4631-90-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>14768.51</v>
+        <v>2043.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1172445-49-CM26</t>
+          <t>2380-1887-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3618.83</v>
+        <v>5620.67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2380-1012-CM26</t>
+          <t>2380-1885-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22747.05</v>
+        <v>11241.33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1027-39-CM26</t>
+          <t>2381-1434-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11506.03</v>
+        <v>962.85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2322-433-CM26</t>
+          <t>2380-2078-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1552.17</v>
+        <v>15877.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2859-576-CM26</t>
+          <t>2380-2083-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1212.93</v>
+        <v>13727.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>751-236-CM26</t>
+          <t>411-9125-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5034.3</v>
+        <v>989.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5349-1418-CM26</t>
+          <t>2380-2195-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1195.19</v>
+        <v>34048.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1027-59-CM26</t>
+          <t>2859-1349-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,2691 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
+        <v>762.79</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2380-2297-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>5867.54</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2923-605-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>977.24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4631-131-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>6257.57</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2380-2541-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3532.09</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5349-2410-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>752.72</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1228-32-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.804.005-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>6206.91</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2380-2634-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>2349.54</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2380-2635-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>7817.98</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5349-2466-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>3018.24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2380-2682-CM25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>35224.59</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>751-1552-CM25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>3681</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2322-1934-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1180.71</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2380-32-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2380-80-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2169.44</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2322-88-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1222.09</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2322-100-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>5181.15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2380-374-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>10406.55</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1554-302-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SEGURYCEL SA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>99.510.910-7</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>9343.16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1554-303-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SEGURYCEL SA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>99.510.910-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>3213.78</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2859-71-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>831.3099999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2381-443-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1400.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2923-280-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>6745.21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>5349-929-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>897.55</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5349-935-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>3259.11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2380-946-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>14260.96</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2381-641-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>796.73</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1027-38-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>34693.59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2322-378-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>793.52</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>904-61-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>3782.26</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2322-393-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>14768.51</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1172445-49-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>3618.83</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2380-1012-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>22747.05</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1027-39-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>11506.03</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2322-433-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1552.17</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2859-576-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1212.93</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>751-236-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>5034.3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5349-1418-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>COMERCIAL COMPARO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1195.19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1027-59-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>23002.61</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2322-602-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5269.42</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1079486-176-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>60.505.105-7</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>2282.64</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3332-93-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>5250.46</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>995-55-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>25982.22</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1028871-512-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.488.070-6</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>36484.16</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1027-74-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>38028.43</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2175-71-CM25</t>
+          <t>2380-789-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11972.91</v>
+        <v>5196.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2380-789-CM25</t>
+          <t>2175-71-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5196.6</v>
+        <v>11972.91</v>
       </c>
     </row>
     <row r="17">
@@ -3259,7 +3259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2380-2297-CM25</t>
+          <t>2923-605-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5867.54</v>
+        <v>977.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2923-605-CM25</t>
+          <t>2380-2297-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>977.24</v>
+        <v>5867.54</v>
       </c>
     </row>
     <row r="49">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1172445-49-CM26</t>
+          <t>2380-1012-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3618.83</v>
+        <v>22747.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2380-1012-CM26</t>
+          <t>1172445-49-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>22747.05</v>
+        <v>3618.83</v>
       </c>
     </row>
     <row r="79">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5938,6 +5938,128 @@
       </c>
       <c r="M90" s="2" t="n">
         <v>38028.43</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2322-722-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>QUALITY RUBBER S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>5825.78</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>411-409-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>1569.94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -928,7 +928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1603,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2095,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2221,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2530,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3083,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3148,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3335,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3461,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3770,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4018,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5242,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5368,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5433,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5742,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6112,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4828,7 +4828,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2381-641-CM26</t>
+          <t>1027-38-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>796.73</v>
+        <v>34693.59</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1027-38-CM26</t>
+          <t>2381-641-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4909,17 +4909,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>34693.59</v>
+        <v>796.73</v>
       </c>
     </row>
     <row r="74">
@@ -5133,7 +5133,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2380-1012-CM26</t>
+          <t>1172445-49-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5173,28 +5173,32 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22747.05</v>
+        <v>3618.83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1172445-49-CM26</t>
+          <t>2380-1012-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5214,17 +5218,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5234,26 +5238,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3618.83</v>
+        <v>22747.05</v>
       </c>
     </row>
     <row r="79">
@@ -5881,7 +5881,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1028871-512-CM26</t>
+          <t>1027-74-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5901,17 +5901,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5936,13 +5936,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>36484.16</v>
+        <v>38028.43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1027-74-CM26</t>
+          <t>1028871-512-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>38028.43</v>
+        <v>36484.16</v>
       </c>
     </row>
     <row r="91">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6124,6 +6124,189 @@
       </c>
       <c r="M92" s="2" t="n">
         <v>1569.94</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1027-99-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>29962.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1027-100-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.330.742-5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>35782.93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2923-779-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>21650.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/atacama.xlsx
@@ -5340,7 +5340,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
